--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122499023</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knarfällan, Skorpetorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6337290</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103021</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -785,7 +780,7 @@
         <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>90828</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,11 +794,6 @@
       </c>
       <c r="E3" t="n">
         <v>5442</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -901,11 +891,6 @@
       </c>
       <c r="E4" t="n">
         <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122484158</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -780,7 +785,7 @@
         <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +799,11 @@
       </c>
       <c r="E3" t="n">
         <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -877,7 +887,7 @@
         <v>122499023</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,6 +901,11 @@
       </c>
       <c r="E4" t="n">
         <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>90859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R2" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R3" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R2" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R3" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>90854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R2" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R3" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>122499023</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B2" t="n">
-        <v>90854</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R2" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R3" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R2" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R3" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R2" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>90960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R3" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>122499023</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>122484305</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60471-2024 artfynd.xlsx
+++ b/artfynd/A 60471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122484158</v>
+        <v>122484305</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584679</v>
+        <v>584640</v>
       </c>
       <c r="R2" t="n">
-        <v>6337322</v>
+        <v>6337411</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122484305</v>
+        <v>122484158</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarfällan, Knarfällan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584640</v>
+        <v>584679</v>
       </c>
       <c r="R3" t="n">
-        <v>6337411</v>
+        <v>6337322</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
